--- a/data/trans_orig/P33B2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33B2_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que se despierta durante la noche y tiene dificultad en volver a dormirse en 2023</t>
+          <t>Población según la frecuencia con la que se despierta durante la noche y tiene dificultad en volver a dormirse en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31812</t>
+          <t>31098</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57169</t>
+          <t>55711</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57972</t>
+          <t>58416</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81160</t>
+          <t>81537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96130</t>
+          <t>92993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>129949</t>
+          <t>128235</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45610</t>
+          <t>45156</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75602</t>
+          <t>74331</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74680</t>
+          <t>74957</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100208</t>
+          <t>101245</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127742</t>
+          <t>126829</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165752</t>
+          <t>165520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108943</t>
+          <t>109411</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>146919</t>
+          <t>149349</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>164186</t>
+          <t>165127</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>198933</t>
+          <t>198832</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>284592</t>
+          <t>282794</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>335782</t>
+          <t>336248</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>382649</t>
+          <t>378329</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>433138</t>
+          <t>431071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>315118</t>
+          <t>315768</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>355970</t>
+          <t>359017</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>711691</t>
+          <t>709283</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>778393</t>
+          <t>778066</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,43%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28752</t>
+          <t>27390</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76058</t>
+          <t>77181</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>88396</t>
+          <t>86620</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>117602</t>
+          <t>119239</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>101745</t>
+          <t>105508</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>186651</t>
+          <t>186181</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37011</t>
+          <t>33528</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98512</t>
+          <t>96983</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98403</t>
+          <t>98441</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130776</t>
+          <t>130838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124337</t>
+          <t>126679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>220175</t>
+          <t>218193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85905</t>
+          <t>79713</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>206693</t>
+          <t>207721</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>209283</t>
+          <t>208612</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250761</t>
+          <t>250404</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264337</t>
+          <t>251617</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>446363</t>
+          <t>450529</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>824399</t>
+          <t>823769</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1035674</t>
+          <t>1060305</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>484314</t>
+          <t>487905</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>536532</t>
+          <t>539099</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1313965</t>
+          <t>1312658</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1648029</t>
+          <t>1664019</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32179</t>
+          <t>33252</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59988</t>
+          <t>62668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25415</t>
+          <t>22715</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70579</t>
+          <t>71084</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61172</t>
+          <t>64914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>117906</t>
+          <t>121346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29507</t>
+          <t>29641</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53485</t>
+          <t>52762</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47671</t>
+          <t>41841</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>119999</t>
+          <t>117612</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>83225</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154018</t>
+          <t>153907</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>122991</t>
+          <t>123062</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>167130</t>
+          <t>168300</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>184217</t>
+          <t>182402</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>609094</t>
+          <t>637401</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,47 +2144,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>19,54%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>68,29%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>499454</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>323353</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>866148</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>30,49%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>19,74%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>65,26%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>499454</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>326984</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>889265</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>30,49%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>19,96%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>449313</t>
+          <t>449321</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>502742</t>
+          <t>503754</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>240440</t>
+          <t>229719</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>578720</t>
+          <t>582153</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>586984</t>
+          <t>617981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1061251</t>
+          <t>1066710</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>65,12%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53705</t>
+          <t>52685</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81823</t>
+          <t>81738</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86702</t>
+          <t>85201</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>127884</t>
+          <t>127834</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>150440</t>
+          <t>149930</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>199699</t>
+          <t>199655</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62874</t>
+          <t>61017</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93398</t>
+          <t>91696</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>102671</t>
+          <t>104315</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>150929</t>
+          <t>151493</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>178499</t>
+          <t>179214</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>230080</t>
+          <t>229777</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>137765</t>
+          <t>138403</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>185425</t>
+          <t>184365</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>181624</t>
+          <t>180168</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>252784</t>
+          <t>253371</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>339995</t>
+          <t>338728</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>425160</t>
+          <t>422726</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>594857</t>
+          <t>593783</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>652776</t>
+          <t>653588</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>586082</t>
+          <t>582986</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>721488</t>
+          <t>714730</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1196829</t>
+          <t>1202552</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1336063</t>
+          <t>1336474</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>164450</t>
+          <t>164739</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>240846</t>
+          <t>241932</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>272533</t>
+          <t>263960</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>368388</t>
+          <t>369815</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>464362</t>
+          <t>471457</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>591541</t>
+          <t>596950</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>191402</t>
+          <t>193285</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>282418</t>
+          <t>279149</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>338174</t>
+          <t>342095</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>458051</t>
+          <t>464038</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>577240</t>
+          <t>585885</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>722211</t>
+          <t>726489</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>446576</t>
+          <t>455661</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>648589</t>
+          <t>656590</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>817813</t>
+          <t>818927</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1480652</t>
+          <t>1552193</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1365154</t>
+          <t>1375464</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2119739</t>
+          <t>2165804</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2316502</t>
+          <t>2315878</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2669232</t>
+          <t>2660483</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1552200</t>
+          <t>1531210</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2061828</t>
+          <t>2059356</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3943748</t>
+          <t>3957080</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4594389</t>
+          <t>4592467</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33B2_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>42204</t>
+          <t>46627</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31098</t>
+          <t>34502</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55711</t>
+          <t>62490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>68909</t>
+          <t>77204</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58416</t>
+          <t>65282</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81537</t>
+          <t>91104</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>111113</t>
+          <t>123831</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92993</t>
+          <t>103812</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>128235</t>
+          <t>142415</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58145</t>
+          <t>63410</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45156</t>
+          <t>51230</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74331</t>
+          <t>83521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,67 +873,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87131</t>
+          <t>94613</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74957</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101245</t>
+          <t>109527</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>11,17%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>14,96%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>158023</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>137904</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>181533</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>11,11%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>15,0%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>145275</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>126829</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>165520</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>127316</t>
+          <t>137894</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109411</t>
+          <t>118539</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>149349</t>
+          <t>159218</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>182127</t>
+          <t>192855</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>165127</t>
+          <t>176418</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>198832</t>
+          <t>210790</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>309443</t>
+          <t>330749</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>282794</t>
+          <t>303389</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>336248</t>
+          <t>359815</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>406747</t>
+          <t>441697</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>378329</t>
+          <t>413891</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>431071</t>
+          <t>465460</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>336701</t>
+          <t>367511</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>315768</t>
+          <t>342899</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>359017</t>
+          <t>390230</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>743448</t>
+          <t>809208</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>709283</t>
+          <t>774765</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>778066</t>
+          <t>847019</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,57%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>674867</t>
+          <t>732183</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>674867</t>
+          <t>732183</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>674867</t>
+          <t>732183</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1309279</t>
+          <t>1421811</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1309279</t>
+          <t>1421811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1309279</t>
+          <t>1421811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54767</t>
+          <t>61936</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27390</t>
+          <t>48146</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77181</t>
+          <t>79238</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>4,59%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>102075</t>
+          <t>112962</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86620</t>
+          <t>96038</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119239</t>
+          <t>129941</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>156842</t>
+          <t>174897</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>105508</t>
+          <t>153046</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>186181</t>
+          <t>200084</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>70960</t>
+          <t>77297</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33528</t>
+          <t>61275</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96983</t>
+          <t>98464</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>113922</t>
+          <t>124983</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98441</t>
+          <t>107691</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130838</t>
+          <t>145330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>184882</t>
+          <t>202281</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126679</t>
+          <t>178065</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>218193</t>
+          <t>227907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>156839</t>
+          <t>182625</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79713</t>
+          <t>157695</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>207721</t>
+          <t>208382</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>230050</t>
+          <t>250894</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>208612</t>
+          <t>229295</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250404</t>
+          <t>273543</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>386889</t>
+          <t>433518</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>251617</t>
+          <t>397285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>450529</t>
+          <t>467133</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>910299</t>
+          <t>727060</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>823769</t>
+          <t>695770</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1060305</t>
+          <t>756866</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>512059</t>
+          <t>581999</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>487905</t>
+          <t>551811</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>539099</t>
+          <t>612724</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1422358</t>
+          <t>1309059</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1312658</t>
+          <t>1267181</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1664019</t>
+          <t>1358332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>64,08%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>44888</t>
+          <t>48976</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33252</t>
+          <t>36714</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62668</t>
+          <t>66223</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50655</t>
+          <t>61416</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22715</t>
+          <t>49838</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71084</t>
+          <t>76410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>95543</t>
+          <t>110393</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64914</t>
+          <t>90694</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121346</t>
+          <t>133217</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39778</t>
+          <t>44146</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29641</t>
+          <t>32589</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52762</t>
+          <t>58741</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>86509</t>
+          <t>101937</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41841</t>
+          <t>85153</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>117612</t>
+          <t>119220</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>126287</t>
+          <t>146083</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>83225</t>
+          <t>126243</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>153907</t>
+          <t>168152</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>144337</t>
+          <t>167279</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>123062</t>
+          <t>144938</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>168300</t>
+          <t>193886</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>355118</t>
+          <t>180535</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>182402</t>
+          <t>156584</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>637401</t>
+          <t>202014</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>499454</t>
+          <t>347814</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>323353</t>
+          <t>318689</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>866148</t>
+          <t>383793</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>475677</t>
+          <t>542671</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>449321</t>
+          <t>510841</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>503754</t>
+          <t>570061</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>441084</t>
+          <t>468371</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>229719</t>
+          <t>442268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>582153</t>
+          <t>493874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>916762</t>
+          <t>1011042</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>617981</t>
+          <t>967138</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1066710</t>
+          <t>1051999</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,13%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>66130</t>
+          <t>72330</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52685</t>
+          <t>56833</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81738</t>
+          <t>87574</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>109576</t>
+          <t>125602</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>85201</t>
+          <t>108874</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>127834</t>
+          <t>145442</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>175706</t>
+          <t>197931</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>149930</t>
+          <t>175608</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>199655</t>
+          <t>222139</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>76924</t>
+          <t>77999</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61017</t>
+          <t>63227</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91696</t>
+          <t>95063</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>129148</t>
+          <t>141557</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>104315</t>
+          <t>124017</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>151493</t>
+          <t>162788</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>206072</t>
+          <t>219555</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>179214</t>
+          <t>196052</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>229777</t>
+          <t>247568</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>160576</t>
+          <t>172675</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>138403</t>
+          <t>149288</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>184365</t>
+          <t>200117</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>226666</t>
+          <t>250008</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>180168</t>
+          <t>227797</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>253371</t>
+          <t>273084</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>387242</t>
+          <t>422683</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>338728</t>
+          <t>390505</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>422726</t>
+          <t>456457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>623201</t>
+          <t>667059</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>593783</t>
+          <t>633369</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>653588</t>
+          <t>696457</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>627203</t>
+          <t>601152</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>582986</t>
+          <t>570843</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>714730</t>
+          <t>628194</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1250404</t>
+          <t>1268211</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1202552</t>
+          <t>1226777</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1336474</t>
+          <t>1310061</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>207989</t>
+          <t>229868</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>164739</t>
+          <t>200258</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>241932</t>
+          <t>257390</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>331214</t>
+          <t>377184</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>263960</t>
+          <t>349499</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>369815</t>
+          <t>407118</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>539203</t>
+          <t>607052</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>471457</t>
+          <t>568166</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>596950</t>
+          <t>653772</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>245807</t>
+          <t>262852</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>193285</t>
+          <t>231205</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>279149</t>
+          <t>295881</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>416710</t>
+          <t>463090</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>342095</t>
+          <t>430619</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>464038</t>
+          <t>498257</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>662517</t>
+          <t>725942</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>585885</t>
+          <t>682668</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>726489</t>
+          <t>772046</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>589067</t>
+          <t>660472</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>455661</t>
+          <t>615675</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>656590</t>
+          <t>709661</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>993961</t>
+          <t>874292</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>818927</t>
+          <t>832242</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1552193</t>
+          <t>918950</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1583027</t>
+          <t>1534764</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1375464</t>
+          <t>1473557</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2165804</t>
+          <t>1606054</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2415925</t>
+          <t>2378487</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2315878</t>
+          <t>2321435</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2660483</t>
+          <t>2433625</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1917047</t>
+          <t>2019033</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1531210</t>
+          <t>1967762</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2059356</t>
+          <t>2071888</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>4332971</t>
+          <t>4397520</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3957080</t>
+          <t>4314385</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4592467</t>
+          <t>4478098</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>61,64%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
